--- a/Thesis Forecasting/metadata/overall_comparison/plant_level_testing_comparison.xlsx
+++ b/Thesis Forecasting/metadata/overall_comparison/plant_level_testing_comparison.xlsx
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RBFNN</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -476,25 +476,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>158</v>
+        <v>234</v>
       </c>
       <c r="D2" t="n">
-        <v>3.475919113707131</v>
+        <v>3.377216762221778</v>
       </c>
       <c r="E2" t="n">
-        <v>1.840847984937388</v>
+        <v>1.83697522051419</v>
       </c>
       <c r="F2" t="n">
-        <v>3.440295102101322</v>
+        <v>3.3902379831123</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8988599585985897</v>
+        <v>0.9017817700204243</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -503,25 +503,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="D3" t="n">
-        <v>3.486362417005194</v>
+        <v>3.393549742790847</v>
       </c>
       <c r="E3" t="n">
-        <v>1.875336494578505</v>
+        <v>1.838306842486888</v>
       </c>
       <c r="F3" t="n">
-        <v>3.427619689013735</v>
+        <v>3.313260015069622</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8996038657827569</v>
+        <v>0.9061913747309848</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RBFNN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="D4" t="n">
-        <v>3.572705810229515</v>
+        <v>3.476164999616764</v>
       </c>
       <c r="E4" t="n">
-        <v>1.928287727407958</v>
+        <v>1.841105299238234</v>
       </c>
       <c r="F4" t="n">
-        <v>3.507520889972095</v>
+        <v>3.440686379843341</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8948686441752667</v>
+        <v>0.8988369512132961</v>
       </c>
     </row>
     <row r="5">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="D5" t="n">
         <v>1.372393407127368</v>
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D6" t="n">
-        <v>2.161182022518592</v>
+        <v>2.360647957762337</v>
       </c>
       <c r="E6" t="n">
-        <v>1.933811975752544</v>
+        <v>2.057751859712116</v>
       </c>
       <c r="F6" t="n">
-        <v>5.005367101266894</v>
+        <v>4.894579628714905</v>
       </c>
       <c r="G6" t="n">
-        <v>0.904776404097143</v>
+        <v>0.9089450616528172</v>
       </c>
     </row>
     <row r="7">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D7" t="n">
-        <v>2.553581038972992</v>
+        <v>2.596536026075724</v>
       </c>
       <c r="E7" t="n">
-        <v>2.173190188862365</v>
+        <v>2.346439887403684</v>
       </c>
       <c r="F7" t="n">
-        <v>5.219189186025636</v>
+        <v>5.164883681643188</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8964670027188831</v>
+        <v>0.8986103092469176</v>
       </c>
     </row>
     <row r="8">
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6106872916793786</v>
+        <v>0.6106872916782813</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6974508930056273</v>
+        <v>0.6974508930041152</v>
       </c>
       <c r="F8" t="n">
-        <v>3.077447039614186</v>
+        <v>3.07744703961429</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9453153141242143</v>
+        <v>0.9453153141242105</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -665,25 +665,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>1.05126148122372</v>
+        <v>0.8368764813740764</v>
       </c>
       <c r="E9" t="n">
-        <v>1.26574175268856</v>
+        <v>0.9950894832429902</v>
       </c>
       <c r="F9" t="n">
-        <v>3.272789934700768</v>
+        <v>2.926018781429621</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9381526910348479</v>
+        <v>0.9505645189020273</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -692,19 +692,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>1.164311265066937</v>
+        <v>1.152639285327153</v>
       </c>
       <c r="E10" t="n">
-        <v>1.365183498334776</v>
+        <v>1.433715598698781</v>
       </c>
       <c r="F10" t="n">
-        <v>3.454070031467231</v>
+        <v>3.117158386064567</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9311114849194968</v>
+        <v>0.943894907113505</v>
       </c>
     </row>
     <row r="11">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="D11" t="n">
         <v>4.039603029011061</v>
@@ -746,19 +746,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D12" t="n">
-        <v>4.200484513643534</v>
+        <v>4.08064247874045</v>
       </c>
       <c r="E12" t="n">
-        <v>1.598433789599624</v>
+        <v>1.572321523955471</v>
       </c>
       <c r="F12" t="n">
-        <v>2.268945184641984</v>
+        <v>2.192159151310138</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8932760677734746</v>
+        <v>0.9003773769971353</v>
       </c>
     </row>
     <row r="13">
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D13" t="n">
-        <v>4.227887501466392</v>
+        <v>4.602579242371828</v>
       </c>
       <c r="E13" t="n">
-        <v>1.614116089819198</v>
+        <v>1.810201869515812</v>
       </c>
       <c r="F13" t="n">
-        <v>2.233242150647068</v>
+        <v>2.416508167953064</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8966083555186281</v>
+        <v>0.8789428778386892</v>
       </c>
     </row>
     <row r="14">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>171</v>
+        <v>307</v>
       </c>
       <c r="D14" t="n">
         <v>1.404527208907398</v>
@@ -827,19 +827,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="D15" t="n">
-        <v>19.87941386644245</v>
+        <v>4.14007245328403</v>
       </c>
       <c r="E15" t="n">
-        <v>8.033408364487512</v>
+        <v>2.912237979858503</v>
       </c>
       <c r="F15" t="n">
-        <v>12.19846815910361</v>
+        <v>6.080681074686011</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9560946692216128</v>
+        <v>0.9890903426365119</v>
       </c>
     </row>
     <row r="16">
@@ -854,25 +854,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>307</v>
       </c>
       <c r="D16" t="n">
-        <v>37.5409989513803</v>
+        <v>9.658712339399798</v>
       </c>
       <c r="E16" t="n">
-        <v>14.05841895127159</v>
+        <v>5.270241597014518</v>
       </c>
       <c r="F16" t="n">
-        <v>22.57904593416176</v>
+        <v>7.47642427112801</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8495757572901768</v>
+        <v>0.9835071945146232</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RBFNN</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="D17" t="n">
-        <v>4.209301696521237</v>
+        <v>3.852817953240654</v>
       </c>
       <c r="E17" t="n">
-        <v>1.490988678325157</v>
+        <v>1.354018360421051</v>
       </c>
       <c r="F17" t="n">
-        <v>2.254351155379669</v>
+        <v>1.948228090654059</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9046698091595458</v>
+        <v>0.9288021413168979</v>
       </c>
     </row>
     <row r="18">
@@ -908,25 +908,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D18" t="n">
-        <v>4.294212888621112</v>
+        <v>4.149024259946129</v>
       </c>
       <c r="E18" t="n">
-        <v>1.526733463455669</v>
+        <v>1.47161523248911</v>
       </c>
       <c r="F18" t="n">
-        <v>2.174929166543046</v>
+        <v>2.076160785216743</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9112685527839555</v>
+        <v>0.9191445501317088</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RBFNN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>29</v>
+        <v>244</v>
       </c>
       <c r="D19" t="n">
-        <v>4.31108012753736</v>
+        <v>4.209301696541133</v>
       </c>
       <c r="E19" t="n">
-        <v>1.542352377302068</v>
+        <v>1.490988678326474</v>
       </c>
       <c r="F19" t="n">
-        <v>2.173520856365352</v>
+        <v>2.254351155380284</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9113834263574155</v>
+        <v>0.9046698091594937</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis Forecasting/metadata/overall_comparison/plant_level_testing_comparison.xlsx
+++ b/Thesis Forecasting/metadata/overall_comparison/plant_level_testing_comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$L$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,16 +415,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="29" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,11 +468,36 @@
           <t>R2</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>evaluation_type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>mape_rows_included</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>mape_rows_excluded</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>mape_rows_excluded_fraction</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>low_load_regime</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>RBFNN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -476,25 +506,42 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="D2" t="n">
-        <v>3.377216762221778</v>
+        <v>5.793521167859188</v>
       </c>
       <c r="E2" t="n">
-        <v>1.83697522051419</v>
+        <v>3.18322446163071</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3902379831123</v>
+        <v>7.967810392425083</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9017817700204243</v>
+        <v>0.4855949283007271</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -503,25 +550,42 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="D3" t="n">
-        <v>3.393549742790847</v>
+        <v>6.215945628090261</v>
       </c>
       <c r="E3" t="n">
-        <v>1.838306842486888</v>
+        <v>3.430201051548947</v>
       </c>
       <c r="F3" t="n">
-        <v>3.313260015069622</v>
+        <v>8.159118872191195</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9061913747309848</v>
+        <v>0.4605964736754846</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RBFNN</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +594,36 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="D4" t="n">
-        <v>3.476164999616764</v>
+        <v>14.89827152521508</v>
       </c>
       <c r="E4" t="n">
-        <v>1.841105299238234</v>
+        <v>8.374156805655712</v>
       </c>
       <c r="F4" t="n">
-        <v>3.440686379843341</v>
+        <v>12.32075573692778</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8988369512132961</v>
+        <v>-0.2299910619096863</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1944</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -557,25 +638,42 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D5" t="n">
-        <v>1.372393407127368</v>
+        <v>5.503947012698498</v>
       </c>
       <c r="E5" t="n">
-        <v>1.163875279835391</v>
+        <v>4.618375436582778</v>
       </c>
       <c r="F5" t="n">
-        <v>4.810318338249981</v>
+        <v>11.22967598524945</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9120531387836908</v>
+        <v>0.516724948633329</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -584,25 +682,42 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D6" t="n">
-        <v>2.360647957762337</v>
+        <v>11.11757252065611</v>
       </c>
       <c r="E6" t="n">
-        <v>2.057751859712116</v>
+        <v>11.08684116555558</v>
       </c>
       <c r="F6" t="n">
-        <v>4.894579628714905</v>
+        <v>15.96858331402931</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9089450616528172</v>
+        <v>0.02277920160870939</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -611,19 +726,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D7" t="n">
-        <v>2.596536026075724</v>
+        <v>13.56293254451962</v>
       </c>
       <c r="E7" t="n">
-        <v>2.346439887403684</v>
+        <v>14.06390543319609</v>
       </c>
       <c r="F7" t="n">
-        <v>5.164883681643188</v>
+        <v>19.57208479661322</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8986103092469176</v>
+        <v>-0.4680271984640838</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -638,25 +770,42 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6106872916782813</v>
+        <v>2.257292839824642</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6974508930041152</v>
+        <v>2.411839192371335</v>
       </c>
       <c r="F8" t="n">
-        <v>3.07744703961429</v>
+        <v>7.954289216601523</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9453153141242105</v>
+        <v>0.6351548356956079</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -665,25 +814,42 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8368764813740764</v>
+        <v>6.021769925483243</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9950894832429902</v>
+        <v>7.438204439875792</v>
       </c>
       <c r="F9" t="n">
-        <v>2.926018781429621</v>
+        <v>10.783571771579</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9505645189020273</v>
+        <v>0.3294500951967373</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -692,19 +858,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>1.152639285327153</v>
+        <v>7.240780251485892</v>
       </c>
       <c r="E10" t="n">
-        <v>1.433715598698781</v>
+        <v>9.178163714670596</v>
       </c>
       <c r="F10" t="n">
-        <v>3.117158386064567</v>
+        <v>11.19566518503113</v>
       </c>
       <c r="G10" t="n">
-        <v>0.943894907113505</v>
+        <v>0.2772208050725247</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -719,25 +902,42 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D11" t="n">
-        <v>4.039603029011061</v>
+        <v>6.914546868482034</v>
       </c>
       <c r="E11" t="n">
-        <v>1.543745650205762</v>
+        <v>2.628291897104535</v>
       </c>
       <c r="F11" t="n">
-        <v>2.189078855121269</v>
+        <v>3.775856572479338</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9006571482808045</v>
+        <v>0.7252522406759934</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -746,25 +946,42 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D12" t="n">
-        <v>4.08064247874045</v>
+        <v>7.531215584620392</v>
       </c>
       <c r="E12" t="n">
-        <v>1.572321523955471</v>
+        <v>2.668592610358417</v>
       </c>
       <c r="F12" t="n">
-        <v>2.192159151310138</v>
+        <v>3.876753823489376</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9003773769971353</v>
+        <v>0.7103726111456587</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -773,19 +990,36 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D13" t="n">
-        <v>4.602579242371828</v>
+        <v>7.681789547555446</v>
       </c>
       <c r="E13" t="n">
-        <v>1.810201869515812</v>
+        <v>2.703064009264373</v>
       </c>
       <c r="F13" t="n">
-        <v>2.416508167953064</v>
+        <v>3.814856253627946</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8789428778386892</v>
+        <v>0.7195473569291837</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -800,25 +1034,42 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="D14" t="n">
-        <v>1.404527208907398</v>
+        <v>6.942901795769707</v>
       </c>
       <c r="E14" t="n">
-        <v>1.395706172839505</v>
+        <v>5.472142688975849</v>
       </c>
       <c r="F14" t="n">
-        <v>5.678938424204445</v>
+        <v>16.54079834570621</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9904842947984128</v>
+        <v>0.9188709960649202</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -827,25 +1078,42 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="D15" t="n">
-        <v>4.14007245328403</v>
+        <v>11.32169312369476</v>
       </c>
       <c r="E15" t="n">
-        <v>2.912237979858503</v>
+        <v>12.22954181132504</v>
       </c>
       <c r="F15" t="n">
-        <v>6.080681074686011</v>
+        <v>22.41959472589807</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9890903426365119</v>
+        <v>0.8509545491074079</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -854,25 +1122,42 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="D16" t="n">
-        <v>9.658712339399798</v>
+        <v>14.76437356829242</v>
       </c>
       <c r="E16" t="n">
-        <v>5.270241597014518</v>
+        <v>16.38180457423511</v>
       </c>
       <c r="F16" t="n">
-        <v>7.47642427112801</v>
+        <v>28.78120354009989</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9835071945146232</v>
+        <v>0.754370167839102</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -881,25 +1166,42 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D17" t="n">
-        <v>3.852817953240654</v>
+        <v>6.65501983293405</v>
       </c>
       <c r="E17" t="n">
-        <v>1.354018360421051</v>
+        <v>2.263569947475957</v>
       </c>
       <c r="F17" t="n">
-        <v>1.948228090654059</v>
+        <v>3.267329231872592</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9288021413168979</v>
+        <v>0.8032523451372638</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>RBFNN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -908,25 +1210,42 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D18" t="n">
-        <v>4.149024259946129</v>
+        <v>7.409128287893188</v>
       </c>
       <c r="E18" t="n">
-        <v>1.47161523248911</v>
+        <v>2.593457805828454</v>
       </c>
       <c r="F18" t="n">
-        <v>2.076160785216743</v>
+        <v>3.495672442815243</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9191445501317088</v>
+        <v>0.7747912657532339</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RBFNN</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -935,23 +1254,40 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="D19" t="n">
-        <v>4.209301696541133</v>
+        <v>8.038243618227868</v>
       </c>
       <c r="E19" t="n">
-        <v>1.490988678326474</v>
+        <v>2.630714025191922</v>
       </c>
       <c r="F19" t="n">
-        <v>2.254351155380284</v>
+        <v>3.667494929248991</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9046698091594937</v>
+        <v>0.7521078284119701</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>rolling_24h_day_ahead_backtest</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1968</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:L19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Thesis Forecasting/metadata/overall_comparison/plant_level_testing_comparison.xlsx
+++ b/Thesis Forecasting/metadata/overall_comparison/plant_level_testing_comparison.xlsx
@@ -424,7 +424,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RBFNN</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -509,16 +509,16 @@
         <v>203</v>
       </c>
       <c r="D2" t="n">
-        <v>5.793521167859188</v>
+        <v>5.815498951255169</v>
       </c>
       <c r="E2" t="n">
-        <v>3.18322446163071</v>
+        <v>3.178357148433609</v>
       </c>
       <c r="F2" t="n">
-        <v>7.967810392425083</v>
+        <v>8.03495817340387</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4855949283007271</v>
+        <v>0.4768882188913155</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>RBFNN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -553,16 +553,16 @@
         <v>203</v>
       </c>
       <c r="D3" t="n">
-        <v>6.215945628090261</v>
+        <v>5.948577545752768</v>
       </c>
       <c r="E3" t="n">
-        <v>3.430201051548947</v>
+        <v>3.275663779475344</v>
       </c>
       <c r="F3" t="n">
-        <v>8.159118872191195</v>
+        <v>8.048516433447602</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4605964736754846</v>
+        <v>0.4751213224448884</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -597,16 +597,16 @@
         <v>203</v>
       </c>
       <c r="D4" t="n">
-        <v>14.89827152521508</v>
+        <v>6.554836238848782</v>
       </c>
       <c r="E4" t="n">
-        <v>8.374156805655712</v>
+        <v>3.511287228809579</v>
       </c>
       <c r="F4" t="n">
-        <v>12.32075573692778</v>
+        <v>8.189139045230684</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2299910619096863</v>
+        <v>0.4566198734553241</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RBFNN</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -641,16 +641,16 @@
         <v>234</v>
       </c>
       <c r="D5" t="n">
-        <v>5.503947012698498</v>
+        <v>5.365430256508413</v>
       </c>
       <c r="E5" t="n">
-        <v>4.618375436582778</v>
+        <v>4.435603963414637</v>
       </c>
       <c r="F5" t="n">
-        <v>11.22967598524945</v>
+        <v>11.56245184173678</v>
       </c>
       <c r="G5" t="n">
-        <v>0.516724948633329</v>
+        <v>0.4876581898627955</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RBFNN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -685,16 +685,16 @@
         <v>234</v>
       </c>
       <c r="D6" t="n">
-        <v>11.11757252065611</v>
+        <v>5.506173843873867</v>
       </c>
       <c r="E6" t="n">
-        <v>11.08684116555558</v>
+        <v>4.620564072948108</v>
       </c>
       <c r="F6" t="n">
-        <v>15.96858331402931</v>
+        <v>11.23351494396772</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02277920160870939</v>
+        <v>0.5163944689125419</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -729,16 +729,16 @@
         <v>234</v>
       </c>
       <c r="D7" t="n">
-        <v>13.56293254451962</v>
+        <v>8.202621515052606</v>
       </c>
       <c r="E7" t="n">
-        <v>14.06390543319609</v>
+        <v>7.774651223153412</v>
       </c>
       <c r="F7" t="n">
-        <v>19.57208479661322</v>
+        <v>13.03510584383248</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4680271984640838</v>
+        <v>0.348837999929106</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -773,16 +773,16 @@
         <v>234</v>
       </c>
       <c r="D8" t="n">
-        <v>2.257292839824642</v>
+        <v>2.257958702419534</v>
       </c>
       <c r="E8" t="n">
-        <v>2.411839192371335</v>
+        <v>2.412928237062234</v>
       </c>
       <c r="F8" t="n">
-        <v>7.954289216601523</v>
+        <v>7.953867317844638</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6351548356956079</v>
+        <v>0.6351935377429914</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>6.021769925483243</v>
+        <v>5.03762304146431</v>
       </c>
       <c r="E9" t="n">
-        <v>7.438204439875792</v>
+        <v>6.128557131679304</v>
       </c>
       <c r="F9" t="n">
-        <v>10.783571771579</v>
+        <v>9.305653959952801</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3294500951967373</v>
+        <v>0.5006562292614767</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -861,16 +861,16 @@
         <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>7.240780251485892</v>
+        <v>5.520566482949032</v>
       </c>
       <c r="E10" t="n">
-        <v>9.178163714670596</v>
+        <v>6.828135371531725</v>
       </c>
       <c r="F10" t="n">
-        <v>11.19566518503113</v>
+        <v>9.591203470101432</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2772208050725247</v>
+        <v>0.4695407249149222</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RBFNN</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -905,16 +905,16 @@
         <v>213</v>
       </c>
       <c r="D11" t="n">
-        <v>6.914546868482034</v>
+        <v>6.892833286714121</v>
       </c>
       <c r="E11" t="n">
-        <v>2.628291897104535</v>
+        <v>2.605220520308225</v>
       </c>
       <c r="F11" t="n">
-        <v>3.775856572479338</v>
+        <v>3.826593723783812</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7252522406759934</v>
+        <v>0.7178189203188657</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RBFNN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -949,16 +949,16 @@
         <v>213</v>
       </c>
       <c r="D12" t="n">
-        <v>7.531215584620392</v>
+        <v>7.014536543223783</v>
       </c>
       <c r="E12" t="n">
-        <v>2.668592610358417</v>
+        <v>2.561916513469902</v>
       </c>
       <c r="F12" t="n">
-        <v>3.876753823489376</v>
+        <v>4.017269162231092</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7103726111456587</v>
+        <v>0.6889966671759968</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -993,16 +993,16 @@
         <v>213</v>
       </c>
       <c r="D13" t="n">
-        <v>7.681789547555446</v>
+        <v>7.507447691170269</v>
       </c>
       <c r="E13" t="n">
-        <v>2.703064009264373</v>
+        <v>2.844720631610776</v>
       </c>
       <c r="F13" t="n">
-        <v>3.814856253627946</v>
+        <v>4.102722877136087</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7195473569291837</v>
+        <v>0.6756248714952823</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1037,16 +1037,16 @@
         <v>276</v>
       </c>
       <c r="D14" t="n">
-        <v>6.942901795769707</v>
+        <v>6.941966326255017</v>
       </c>
       <c r="E14" t="n">
-        <v>5.472142688975849</v>
+        <v>5.470575399659038</v>
       </c>
       <c r="F14" t="n">
-        <v>16.54079834570621</v>
+        <v>16.53993398154544</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9188709960649202</v>
+        <v>0.9188794748782994</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1081,16 +1081,16 @@
         <v>276</v>
       </c>
       <c r="D15" t="n">
-        <v>11.32169312369476</v>
+        <v>8.226158995796979</v>
       </c>
       <c r="E15" t="n">
-        <v>12.22954181132504</v>
+        <v>7.689717487901834</v>
       </c>
       <c r="F15" t="n">
-        <v>22.41959472589807</v>
+        <v>20.04579984119748</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8509545491074079</v>
+        <v>0.8808456260975959</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1125,16 +1125,16 @@
         <v>276</v>
       </c>
       <c r="D16" t="n">
-        <v>14.76437356829242</v>
+        <v>8.226158995796979</v>
       </c>
       <c r="E16" t="n">
-        <v>16.38180457423511</v>
+        <v>7.689717487901834</v>
       </c>
       <c r="F16" t="n">
-        <v>28.78120354009989</v>
+        <v>20.04579984119748</v>
       </c>
       <c r="G16" t="n">
-        <v>0.754370167839102</v>
+        <v>0.8808456260975959</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1169,16 +1169,16 @@
         <v>213</v>
       </c>
       <c r="D17" t="n">
-        <v>6.65501983293405</v>
+        <v>6.778516069692492</v>
       </c>
       <c r="E17" t="n">
-        <v>2.263569947475957</v>
+        <v>2.326595256288697</v>
       </c>
       <c r="F17" t="n">
-        <v>3.267329231872592</v>
+        <v>3.291372438935524</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8032523451372638</v>
+        <v>0.8003460879679845</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1213,16 +1213,16 @@
         <v>213</v>
       </c>
       <c r="D18" t="n">
-        <v>7.409128287893188</v>
+        <v>7.100053092815831</v>
       </c>
       <c r="E18" t="n">
-        <v>2.593457805828454</v>
+        <v>2.470343544306012</v>
       </c>
       <c r="F18" t="n">
-        <v>3.495672442815243</v>
+        <v>3.390199402978767</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7747912657532339</v>
+        <v>0.7881764442358834</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1257,16 +1257,16 @@
         <v>213</v>
       </c>
       <c r="D19" t="n">
-        <v>8.038243618227868</v>
+        <v>7.862272269009213</v>
       </c>
       <c r="E19" t="n">
-        <v>2.630714025191922</v>
+        <v>2.718965435018927</v>
       </c>
       <c r="F19" t="n">
-        <v>3.667494929248991</v>
+        <v>3.843905664536912</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7521078284119701</v>
+        <v>0.7276864764818894</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>

--- a/Thesis Forecasting/metadata/overall_comparison/plant_level_testing_comparison.xlsx
+++ b/Thesis Forecasting/metadata/overall_comparison/plant_level_testing_comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$L$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$G$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -425,11 +425,6 @@
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="29" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,31 +463,6 @@
           <t>R2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>evaluation_type</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>mape_rows_included</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>mape_rows_excluded</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>mape_rows_excluded_fraction</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>low_load_regime</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -520,23 +490,6 @@
       <c r="G2" t="n">
         <v>0.4768882188913155</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.01219512195121951</v>
-      </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -564,23 +517,6 @@
       <c r="G3" t="n">
         <v>0.4751213224448884</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J3" t="n">
-        <v>24</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.01219512195121951</v>
-      </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -608,23 +544,6 @@
       <c r="G4" t="n">
         <v>0.4566198734553241</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1944</v>
-      </c>
-      <c r="J4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.01219512195121951</v>
-      </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -652,23 +571,6 @@
       <c r="G5" t="n">
         <v>0.4876581898627955</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -696,23 +598,6 @@
       <c r="G6" t="n">
         <v>0.5163944689125419</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -740,23 +625,6 @@
       <c r="G7" t="n">
         <v>0.348837999929106</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -784,23 +652,6 @@
       <c r="G8" t="n">
         <v>0.6351935377429914</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -828,23 +679,6 @@
       <c r="G9" t="n">
         <v>0.5006562292614767</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -872,23 +706,6 @@
       <c r="G10" t="n">
         <v>0.4695407249149222</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -916,23 +733,6 @@
       <c r="G11" t="n">
         <v>0.7178189203188657</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -960,23 +760,6 @@
       <c r="G12" t="n">
         <v>0.6889966671759968</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1004,23 +787,6 @@
       <c r="G13" t="n">
         <v>0.6756248714952823</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1048,23 +814,6 @@
       <c r="G14" t="n">
         <v>0.9188794748782994</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1092,23 +841,6 @@
       <c r="G15" t="n">
         <v>0.8808456260975959</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1136,23 +868,6 @@
       <c r="G16" t="n">
         <v>0.8808456260975959</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1180,23 +895,6 @@
       <c r="G17" t="n">
         <v>0.8003460879679845</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1224,23 +922,6 @@
       <c r="G18" t="n">
         <v>0.7881764442358834</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1268,26 +949,9 @@
       <c r="G19" t="n">
         <v>0.7276864764818894</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>rolling_24h_day_ahead_backtest</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1968</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="b">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L19"/>
+  <autoFilter ref="A1:G19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Thesis Forecasting/metadata/overall_comparison/plant_level_testing_comparison.xlsx
+++ b/Thesis Forecasting/metadata/overall_comparison/plant_level_testing_comparison.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,37 +440,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>plant</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>feature_count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MAPE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MAE</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
